--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/pre LAM_HRM-2031-0240/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.89234</v>
+        <v>17.49246</v>
       </c>
       <c r="D2" t="n">
-        <v>17.69682</v>
+        <v>17.13051</v>
       </c>
       <c r="E2" t="n">
-        <v>17.47206</v>
+        <v>17.2004</v>
       </c>
       <c r="F2" t="n">
-        <v>45.13132</v>
+        <v>44.42006</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05291</v>
+        <v>0.05236</v>
       </c>
       <c r="H2" t="n">
-        <v>1.87465</v>
+        <v>1.89336</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.76595</v>
+        <v>17.58419</v>
       </c>
       <c r="D3" t="n">
-        <v>17.00716</v>
+        <v>17.37068</v>
       </c>
       <c r="E3" t="n">
-        <v>17.15031</v>
+        <v>17.55868</v>
       </c>
       <c r="F3" t="n">
-        <v>45.73906</v>
+        <v>44.14169</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0512</v>
+        <v>0.05299</v>
       </c>
       <c r="H3" t="n">
-        <v>1.90449</v>
+        <v>1.92721</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.19637</v>
+        <v>17.6544</v>
       </c>
       <c r="D4" t="n">
-        <v>16.85834</v>
+        <v>17.56319</v>
       </c>
       <c r="E4" t="n">
-        <v>17.21406</v>
+        <v>17.56492</v>
       </c>
       <c r="F4" t="n">
-        <v>43.70873</v>
+        <v>45.11345</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0535</v>
+        <v>0.05308</v>
       </c>
       <c r="H4" t="n">
-        <v>1.91899</v>
+        <v>1.89764</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.16997</v>
+        <v>17.54611</v>
       </c>
       <c r="D6" t="n">
-        <v>16.69551</v>
+        <v>16.69124</v>
       </c>
       <c r="E6" t="n">
-        <v>17.18412</v>
+        <v>17.45307</v>
       </c>
       <c r="F6" t="n">
-        <v>22.93181</v>
+        <v>23.08231</v>
       </c>
       <c r="G6" t="n">
-        <v>36.18047</v>
+        <v>35.48608</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.50724</v>
+        <v>17.53429</v>
       </c>
       <c r="D7" t="n">
-        <v>16.81714</v>
+        <v>16.73734</v>
       </c>
       <c r="E7" t="n">
-        <v>16.91624</v>
+        <v>17.13861</v>
       </c>
       <c r="F7" t="n">
-        <v>22.59531</v>
+        <v>22.76858</v>
       </c>
       <c r="G7" t="n">
-        <v>36.20798</v>
+        <v>36.24949</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.31543</v>
+        <v>17.26101</v>
       </c>
       <c r="D8" t="n">
-        <v>16.66539</v>
+        <v>16.89382</v>
       </c>
       <c r="E8" t="n">
-        <v>17.08466</v>
+        <v>17.25358</v>
       </c>
       <c r="F8" t="n">
-        <v>22.69051</v>
+        <v>22.83</v>
       </c>
       <c r="G8" t="n">
-        <v>35.70266</v>
+        <v>35.43177</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.63761</v>
+        <v>0.63208</v>
       </c>
       <c r="D10" t="n">
-        <v>1.14894</v>
+        <v>1.15772</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.63523</v>
+        <v>0.64542</v>
       </c>
       <c r="D11" t="n">
-        <v>1.14988</v>
+        <v>1.1381</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.63686</v>
+        <v>0.6408199999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>1.19087</v>
+        <v>1.16828</v>
       </c>
     </row>
   </sheetData>
